--- a/HistóricoDoMeuExperimento.xlsx
+++ b/HistóricoDoMeuExperimento.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario1\Documents\mestrado\ia\at2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F80C85B-DB70-4643-9F6B-6C6A6A33123C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB139C5-11BE-4E7B-B9B2-5A3A2E499C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>Model Name and Version - Agent Name - Skills and Agents</t>
   </si>
@@ -40,30 +40,76 @@
     <t>Observations</t>
   </si>
   <si>
-    <t xml:space="preserve"> vamos fazer um sistema, vou te passar alguns requisitos e vc vai fazendo. O sistema deve ser uma aplicação web com 
-  cliente React em Typescript, e o servidor Node também                                                              
-  em Typescript. Para cenários, use a linguagem Gherkin do Cucumber, que deve ser usado para                         
-  implementar os testes de aceitação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> primeiro requisito: Gerenciamento (inclusão, alteração e remoção) de questões fechadas de provas. Cada
-  questão tem um enunciado e um conjunto de alternativas. Cada alternativa tem a sua
-  descrição e a indicação de se ela deve ser marcada ou não pelo aluno.</t>
-  </si>
-  <si>
     <t>nenhum</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
-    <t>Pretendo usar em outras abordagens</t>
-  </si>
-  <si>
-    <t>Não criou a estrutura de forma correta</t>
-  </si>
-  <si>
-    <t>Ruim</t>
+    <t xml:space="preserve">eu quero fazer um sistema, vou dividir em alguns requisitos e vou te passar. aqui vai o primeiro requisido do 
+sistema: Basicamente, o sistema a ser desenvolvido deve implementar as seguintes funcionalidades              
+principais:1. Gerenciamento (inclusão, alteração e remoção) de alunos, com uma página específica com a        
+lista de alunos cadastrados. Cada aluno deve ter o seu nome, CPF, e email.                                    
+O sistema deve ser uma aplicação web com cliente React em Typescript, e o servidor Node também                
+em Typescript. Para cenários, use a linguagem Gherkin do Cucumber, que deve ser usado para                    
+implementar os testes de aceitação. </t>
+  </si>
+  <si>
+    <t>bom</t>
+  </si>
+  <si>
+    <t>Ele entregou tudo dentro dos conformes</t>
+  </si>
+  <si>
+    <t>Senti falta de uns detalhes bobos, mas que fazem diferença na usabilidade, tipo uma formatação no campo de CPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> agora vamos para o segundo requisito: Numa outra página, o sistema deve permitir o gerenciamento das avaliações
+  dos alunos,
+  mostrando uma tabela com os nomes dos alunos na primeira coluna, e para cada aluno as
+  suas avaliações em várias metas (Requisitos, Testes, etc.). Cada meta em uma coluna
+  diferente. As avaliações são indicadas pelos conceitos MANA, MPA, ou MA, que
+  respectivamente indicam Meta Ainda Não Atingida, Meta Parcialmente Atingida, e Meta
+  Atingida.
+  Persistência (via JSON) do cadastro de alunos e suas avaliações nas várias metas.</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Ele fez a tabela de forma correta</t>
+  </si>
+  <si>
+    <t>Eu não entendi muito bem esse requisito no PDF da atividade, então não consigo avaliar o retorno com tanta precisão, mas acredito que foi feito da forma correta.</t>
+  </si>
+  <si>
+    <t>agora vamos para o proximo requisito: Gerenciamento (inclusão, alteração e remoção) de turmas. Cada turma contém a
+descrição
+do seu tópico (por exemplo, Introdução a Programação), o ano, o semestre, os alunos
+matriculados na mesma, e as informações das avaliações desses alunos naquela turma. Deve
+ser possível visualizar cada turma com seus alunos e avaliações separadamente.</t>
+  </si>
+  <si>
+    <t>mais ou menos</t>
+  </si>
+  <si>
+    <t>Ele fez o que eu pedia no requisito</t>
+  </si>
+  <si>
+    <t>Ele fez o que foi pedido, mas acredito que ficou dificil de entender a usabilidade dos campos. No incio achei até que era bug, revisei o codigo e não achei nenhum motivo aparente pra não estar funcionando, aí saí testando a tela manualmente até entender como funcionava os campos e descobrir que não era bug mas sim problema de usabilidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vamos para o proximo requisito: Envio de email para um aluno quando o professor preencher ou alterar a avaliação
+  do aluno
+  para alguma meta. Para evitar que o aluno receba muitos emails (caso o professor digite
+  várias avaliações num mesmo dia), enviar apenas um email por dia com todas as avaliações
+  modificadas, nas várias turmas em que aquele aluno está matriculado. </t>
+  </si>
+  <si>
+    <t>problema do email</t>
+  </si>
+  <si>
+    <t>Ele aparentemente fez tudo, mas tô em duvida sobre o envio de email</t>
   </si>
 </sst>
 </file>
@@ -1492,12 +1538,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="105.6">
+    <row r="3" spans="1:5" ht="198">
       <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>9</v>
@@ -1505,34 +1551,60 @@
       <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" ht="92.4">
+      <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="198">
       <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="145.19999999999999">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="132">
+      <c r="A6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="7"/>
